--- a/sources/ling_step2.xlsx
+++ b/sources/ling_step2.xlsx
@@ -422,7 +422,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4054,7 +4054,7 @@
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
